--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Desktop\設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4750CFE9-631A-4B55-B8ED-840DF87601BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B42F3A-CC37-429D-8630-7A91E06C14CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1292,19 +1292,82 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1317,18 +1380,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1346,55 +1397,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1412,11 +1415,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1430,13 +1448,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1448,23 +1460,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1472,32 +1490,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1653,22 +1653,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>933450</xdr:colOff>
+      <xdr:colOff>769967</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>6657</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
+      <xdr:colOff>511969</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>188793</xdr:rowOff>
+      <xdr:rowOff>160944</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE85622B-D325-C72E-6B0F-39CEC9349C41}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C90233-EB62-8BE8-1639-834EBF600A2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1691,8 +1691,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3076575" y="1552575"/>
-          <a:ext cx="3048000" cy="1779468"/>
+          <a:off x="2924998" y="1530657"/>
+          <a:ext cx="3099565" cy="1725912"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1921,85 +1921,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2019,46 +2019,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="73" t="s">
+      <c r="G13" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="73" t="s">
+      <c r="H13" s="45"/>
+      <c r="I13" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="42"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="73"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="42"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="73"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="42"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2067,13 +2067,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="74" t="s">
+      <c r="G17" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3087,19 +3087,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3111,192 +3111,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="94">
+      <c r="G2" s="51"/>
+      <c r="H2" s="81">
         <v>46125</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="78" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="69"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="38" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="38" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="38" t="s">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="47"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="79" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="47"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="88"/>
-      <c r="B10" s="90" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="89"/>
-      <c r="B11" s="90" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="79" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="47"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="38" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="47"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="80" t="s">
+      <c r="A13" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="65"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="42"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4287,17 +4287,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4306,14 +4303,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4332,19 +4332,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4356,48 +4356,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="95">
+      <c r="G2" s="51"/>
+      <c r="H2" s="96">
         <v>46125</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5754,19 +5754,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5778,48 +5778,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="106">
+      <c r="G2" s="51"/>
+      <c r="H2" s="54">
         <v>46125</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="68"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7170,19 +7170,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -7194,188 +7194,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="106">
+      <c r="G2" s="51"/>
+      <c r="H2" s="54">
         <v>46125</v>
       </c>
-      <c r="I2" s="66"/>
-      <c r="J2" s="68"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="69"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="69"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="69"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="72"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="73"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="73"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="73"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="73"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="73"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="47"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
@@ -7384,11 +7384,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="45"/>
       <c r="D16" s="15" t="s">
         <v>30</v>
       </c>
@@ -7401,18 +7401,18 @@
       <c r="G16" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="47"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="17" t="s">
         <v>80</v>
       </c>
@@ -7423,109 +7423,109 @@
       <c r="G17" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="47"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="45"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="47"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="45"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="47"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="47"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="47"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="42"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="47"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="38" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="42"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="45"/>
       <c r="I25" s="15" t="s">
         <v>28</v>
       </c>
@@ -7534,11 +7534,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="50" t="s">
+      <c r="A26" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="42"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="15" t="s">
         <v>30</v>
       </c>
@@ -7551,18 +7551,18 @@
       <c r="G26" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="40"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="47"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="42"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="17" t="s">
         <v>82</v>
       </c>
@@ -7573,83 +7573,83 @@
       <c r="G27" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="38" t="s">
+      <c r="H27" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="47"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="42"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="47"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="42"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="47"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="42"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="47"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="42"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="45"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="40"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="47"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="42"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="45"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="40"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="47"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="47"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="49"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="65"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="42"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8620,30 +8620,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8660,16 +8646,30 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8689,182 +8689,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="52"/>
+      <c r="T1" s="69"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="55"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="72"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="58"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="73"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="93"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="104"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="101"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="78" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="52"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="69"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="38" t="s">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="40"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="44"/>
+      <c r="S6" s="44"/>
+      <c r="T6" s="47"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="38" t="s">
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="40"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="47"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9063,37 +9063,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="103" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="59" t="s">
+      <c r="D15" s="45"/>
+      <c r="E15" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="59" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="59" t="s">
+      <c r="H15" s="44"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="59" t="s">
+      <c r="K15" s="45"/>
+      <c r="L15" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="59" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="45"/>
+      <c r="O15" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="42"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="45"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
@@ -9105,37 +9105,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="96">
+      <c r="A16" s="102">
         <v>1</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="97" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="97" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="102" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="102" t="s">
+      <c r="H16" s="44"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="100" t="s">
+      <c r="K16" s="45"/>
+      <c r="L16" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="100" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="42"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -9147,37 +9147,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="96">
+      <c r="A17" s="102">
         <v>2</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="97" t="s">
+      <c r="B17" s="45"/>
+      <c r="C17" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="97" t="s">
+      <c r="D17" s="45"/>
+      <c r="E17" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="102" t="s">
+      <c r="F17" s="45"/>
+      <c r="G17" s="97" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="102" t="s">
+      <c r="H17" s="44"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="42"/>
-      <c r="L17" s="100" t="s">
+      <c r="K17" s="45"/>
+      <c r="L17" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="100" t="s">
+      <c r="M17" s="44"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="99" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="42"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="45"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9189,23 +9189,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="96"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="42"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="44"/>
+      <c r="Q18" s="45"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9217,23 +9217,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="96"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="102"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="42"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="45"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -9245,23 +9245,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="96"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="42"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="99"/>
+      <c r="P20" s="44"/>
+      <c r="Q20" s="45"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -9273,23 +9273,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="96"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="42"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="45"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -9301,23 +9301,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="96"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="102"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="102"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="100"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="42"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="99"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="45"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -9329,23 +9329,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="96"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="102"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="42"/>
+      <c r="A23" s="102"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="97"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="99"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="45"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9357,23 +9357,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="96"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="42"/>
+      <c r="A24" s="102"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="99"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="99"/>
+      <c r="P24" s="44"/>
+      <c r="Q24" s="45"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9385,23 +9385,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="96"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="42"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="97"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="45"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9413,23 +9413,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="96"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="102"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="102"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="42"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="97"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="99"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="45"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9441,23 +9441,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="96"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="97"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="102"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="102"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="42"/>
+      <c r="A27" s="102"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="97"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="99"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="99"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="45"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9469,23 +9469,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="102"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="102"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="100"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="42"/>
+      <c r="A28" s="102"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="97"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="99"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="45"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9497,23 +9497,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="96"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="102"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="102"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="42"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="97"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="99"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="99"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9525,23 +9525,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="96"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="97"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="102"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="102"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="42"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="97"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="99"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -9553,23 +9553,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="105"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="49"/>
+      <c r="A31" s="105"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="40"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10567,62 +10567,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10647,62 +10647,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Desktop\設計書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B42F3A-CC37-429D-8630-7A91E06C14CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117265E1-4677-4C93-8919-BDED166DF3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,28 +18,24 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
+    <sheet name="画面設計書 (2)" sheetId="7" r:id="rId6"/>
+    <sheet name="画面設計書 (3)" sheetId="8" r:id="rId7"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
-  </si>
-  <si>
-    <t>○○○○システム</t>
   </si>
   <si>
     <t>初版</t>
   </si>
   <si>
     <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -288,88 +284,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>システムはDB上から該当タスクを削除する</t>
-    <rPh sb="7" eb="8">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1．ユーザーが「タスク詳細」画面の「タスク削除」ボタンを選択する
-2．システムが「タスク削除確認」画面を表示する
-3．ユーザーが「タスク削除確認」画面の「タスク削除」ボタンを選択する
-4．タスクの削除に成功した場合、システムが「タスク削除完了」画面を表示する</t>
-    <rPh sb="11" eb="13">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="68" eb="72">
-      <t>サクジョカクニン</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="101" eb="103">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="105" eb="107">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">4a．タスクの削除に失敗した場合、システムが「エラー画面」を表示する
-</t>
-    <rPh sb="7" eb="9">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>①</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -424,6 +338,139 @@
     <t>タスク削除確認画面</t>
     <rPh sb="3" eb="9">
       <t>サクジョカクニンガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">3a1.ユーザーが「タスク削除確認」画面の「戻る」を選択する
+3a2.システムが「タスク詳細」画面を表示する
+4a．タスクの削除に失敗した場合、システムが「エラー画面」を表示する
+</t>
+    <rPh sb="22" eb="23">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskManager62システム</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1．ユーザーがタスク詳細画面のタスク削除を選択する
+2．システムがタスク削除確認画面を表示する
+3．ユーザーがタスクの削除を確定する
+4．タスクの削除に成功した場合、システムがタスク削除完了画面を表示する
+</t>
+    <rPh sb="10" eb="12">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>menu.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面へ</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除完了画面</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除エラー画面</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムはDB上から該当タスクを削除すること</t>
+    <rPh sb="7" eb="8">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1292,6 +1339,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1301,29 +1375,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1338,6 +1415,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1364,42 +1447,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1415,26 +1462,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1448,7 +1480,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1460,20 +1498,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1481,23 +1534,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1653,15 +1700,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>769967</xdr:colOff>
+      <xdr:colOff>1081848</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>6657</xdr:rowOff>
+      <xdr:rowOff>40374</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>511969</xdr:colOff>
+      <xdr:colOff>823850</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>160944</xdr:rowOff>
+      <xdr:rowOff>194661</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1691,8 +1738,74 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2924998" y="1530657"/>
-          <a:ext cx="3099565" cy="1725912"/>
+          <a:off x="3231295" y="1582918"/>
+          <a:ext cx="3079967" cy="1772694"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>803484</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>88538</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>376659</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>162623</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8A34F45-D1F3-291C-B0DD-691D489A5A03}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2964033" y="1645062"/>
+          <a:ext cx="2918541" cy="1677073"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1939,67 +2052,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2020,16 +2133,16 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="78" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
+        <v>84</v>
+      </c>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2037,28 +2150,28 @@
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
       <c r="G13" s="74" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="42"/>
+      <c r="I13" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="74"/>
-      <c r="H14" s="45"/>
+      <c r="H14" s="42"/>
       <c r="I14" s="74"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="74"/>
-      <c r="H15" s="45"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="74"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="45"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2068,12 +2181,12 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
+        <v>81</v>
+      </c>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3087,216 +3200,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="67" t="s">
+      <c r="G1" s="45"/>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="95">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="87" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="81">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="56" t="s">
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="40"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="40"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="88" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="80" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="40"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="89"/>
+      <c r="B10" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="42"/>
+      <c r="D10" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="58"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="94" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="69"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="47"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="47"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="84" t="s">
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="40"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="90"/>
+      <c r="B11" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="95" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="47"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="84" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="40"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="47"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="84" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="47"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="47"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="42"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4287,6 +4400,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4295,25 +4427,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4332,72 +4445,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="67" t="s">
+      <c r="A1" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="51"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
       <c r="H2" s="96">
         <v>46125</v>
       </c>
-      <c r="I2" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="57"/>
+      <c r="I2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="58"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5754,72 +5867,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="67" t="s">
+      <c r="A1" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="54">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
         <v>46125</v>
       </c>
-      <c r="I2" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="57"/>
+      <c r="I2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="58"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7170,486 +7283,486 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="54">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="56"/>
-      <c r="J2" s="57"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="58"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="69"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="70"/>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="72"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="73"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="73"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="73"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="73"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="73"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="73"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="48" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="J15" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="15" t="s">
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="48" t="s">
+      <c r="E16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="47"/>
+      <c r="H16" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
+      <c r="A17" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="47"/>
+        <v>75</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="47"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="47"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="47"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="47"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="47"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="42"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="40"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="47"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48" t="s">
+      <c r="J25" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="15" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J25" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="48" t="s">
+      <c r="E26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="15" t="s">
+      <c r="F26" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="G26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="44"/>
-      <c r="J26" s="47"/>
+      <c r="H26" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="39"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="42"/>
       <c r="D27" s="17" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F27" s="18"/>
       <c r="G27" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="46" t="s">
-        <v>84</v>
-      </c>
-      <c r="I27" s="44"/>
-      <c r="J27" s="47"/>
+        <v>77</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" s="39"/>
+      <c r="J27" s="40"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="42"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="47"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="42"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="47"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="45"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="47"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="45"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="42"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="46"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="47"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="45"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="42"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="47"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="39"/>
+      <c r="J32" s="40"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="38"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="42"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="65"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8620,16 +8733,30 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8646,30 +8773,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8679,6 +8792,2707 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E1A6AD-24AE-4696-B2EE-8A4E4C481296}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J990"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="41"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAAFCE6-8E67-44F1-B2B1-1F1D486C557E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J990"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="45"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="40"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="41"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="40"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="41"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="40"/>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="41"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="41"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="40"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="41"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="40"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
@@ -8689,182 +11503,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="82" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="45"/>
+      <c r="S1" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="52"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="55"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="58"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="105"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="66"/>
-      <c r="S1" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="69"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="72"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="73"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="101"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="64" t="s">
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="52"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="94" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="40"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="69"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="47"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="47"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="40"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8892,11 +11706,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -8926,7 +11740,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -8956,7 +11770,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -8986,7 +11800,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -9016,7 +11830,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -9063,79 +11877,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="104" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="45"/>
-      <c r="E15" s="49" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="49" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="49" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="45"/>
-      <c r="L15" s="49" t="s">
+      <c r="P15" s="39"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="44"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="49" t="s">
+      <c r="S15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="97">
+        <v>1</v>
+      </c>
+      <c r="B16" s="42"/>
+      <c r="C16" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="98" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
-        <v>1</v>
-      </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="103" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="103" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="97" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="97" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="45"/>
-      <c r="L16" s="99" t="s">
-        <v>59</v>
-      </c>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="45"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -9147,37 +11961,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="98" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="42"/>
+      <c r="E17" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="42"/>
+      <c r="G17" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="103" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="97" t="s">
+      <c r="K17" s="42"/>
+      <c r="L17" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="97" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="45"/>
-      <c r="L17" s="99" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="45"/>
-      <c r="O17" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="45"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9189,23 +12003,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="45"/>
+      <c r="A18" s="97"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="101"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9217,23 +12031,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="97"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="99"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="45"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="45"/>
+      <c r="A19" s="97"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="103"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="101"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="42"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -9245,23 +12059,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="45"/>
-      <c r="O20" s="99"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="45"/>
+      <c r="A20" s="97"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="42"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -9273,23 +12087,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="99"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="99"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="45"/>
+      <c r="A21" s="97"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="101"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="42"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -9301,23 +12115,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="99"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="99"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="45"/>
+      <c r="A22" s="97"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="101"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -9329,23 +12143,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="99"/>
-      <c r="P23" s="44"/>
-      <c r="Q23" s="45"/>
+      <c r="A23" s="97"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="103"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9357,23 +12171,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="99"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="45"/>
+      <c r="A24" s="97"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9385,23 +12199,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="45"/>
+      <c r="A25" s="97"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="103"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="101"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9413,23 +12227,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="99"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="99"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="45"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="103"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="101"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="42"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9441,23 +12255,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="97"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="99"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="45"/>
-      <c r="O27" s="99"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="45"/>
+      <c r="A27" s="97"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="101"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="42"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9469,23 +12283,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="97"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="99"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="99"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="45"/>
+      <c r="A28" s="97"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="103"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="101"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="101"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="42"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9497,23 +12311,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="97"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="99"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="45"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="103"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="101"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9525,23 +12339,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="97"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="99"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="99"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="45"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="103"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="101"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="42"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -9553,23 +12367,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="105"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="40"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10567,6 +13381,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10591,118 +13517,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117265E1-4677-4C93-8919-BDED166DF3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA11E54-F909-4317-8E1C-FC767C2020BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -471,6 +471,20 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-delete-confirm.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク削除確認画面に遷移</t>
+    <rPh sb="3" eb="9">
+      <t>サクジョカクニンガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1827,6 +1841,72 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>709307</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>81064</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>415452</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>158357</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9DDC13B-4DD4-CF8F-705E-96492070A44A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2857498" y="1641543"/>
+          <a:ext cx="3050028" cy="1658037"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -10356,7 +10436,7 @@
       <c r="B15" s="39"/>
       <c r="C15" s="42"/>
       <c r="D15" s="38" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
@@ -10366,7 +10446,7 @@
         <v>26</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
@@ -10400,16 +10480,18 @@
       <c r="B17" s="39"/>
       <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>74</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="38"/>
+        <v>75</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>93</v>
+      </c>
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
@@ -11489,6 +11571,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA11E54-F909-4317-8E1C-FC767C2020BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D179BB-9EDD-437F-9081-D2BD54C7BFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -486,6 +486,10 @@
     <rPh sb="10" eb="12">
       <t>センイ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>②</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1353,19 +1357,52 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1376,21 +1413,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1416,7 +1438,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1428,38 +1462,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1476,11 +1480,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1494,13 +1513,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1512,23 +1525,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1536,29 +1555,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1780,22 +1784,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>803484</xdr:colOff>
+      <xdr:colOff>820772</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>88538</xdr:rowOff>
+      <xdr:rowOff>91197</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>376659</xdr:colOff>
+      <xdr:colOff>405319</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>162623</xdr:rowOff>
+      <xdr:rowOff>145482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8A34F45-D1F3-291C-B0DD-691D489A5A03}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB7C19F9-BA0A-1FC5-B0DB-423696209143}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1818,8 +1822,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2964033" y="1645062"/>
-          <a:ext cx="2918541" cy="1677073"/>
+          <a:off x="2968963" y="1651676"/>
+          <a:ext cx="2928430" cy="1635029"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1846,22 +1850,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>709307</xdr:colOff>
+      <xdr:colOff>694532</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>81064</xdr:rowOff>
+      <xdr:rowOff>148827</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>415452</xdr:colOff>
+      <xdr:colOff>492658</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>158357</xdr:rowOff>
+      <xdr:rowOff>228203</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9DDC13B-4DD4-CF8F-705E-96492070A44A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{694432C0-FCC8-88A0-8340-A95E930A29E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1884,8 +1888,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2857498" y="1641543"/>
-          <a:ext cx="3050028" cy="1658037"/>
+          <a:off x="2847579" y="1686718"/>
+          <a:ext cx="3131876" cy="1686719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2132,67 +2136,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2215,14 +2219,14 @@
       <c r="E8" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2232,26 +2236,26 @@
       <c r="G13" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="42"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="74" t="s">
         <v>2</v>
       </c>
       <c r="J13" s="39"/>
-      <c r="K13" s="42"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="74"/>
-      <c r="H14" s="42"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="74"/>
       <c r="J14" s="39"/>
-      <c r="K14" s="42"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="74"/>
-      <c r="H15" s="42"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="74"/>
       <c r="J15" s="39"/>
-      <c r="K15" s="42"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2263,10 +2267,10 @@
       <c r="G17" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3280,19 +3284,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -3304,72 +3308,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="95">
+      <c r="G2" s="71"/>
+      <c r="H2" s="81">
         <v>46125</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="85" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="39"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="40"/>
+      <c r="D6" s="41" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="39"/>
@@ -3377,15 +3381,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="85" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="39"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="40"/>
+      <c r="D7" s="41" t="s">
         <v>67</v>
       </c>
       <c r="E7" s="39"/>
@@ -3393,15 +3397,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
+      <c r="J7" s="42"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="85" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="39"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="38" t="s">
+      <c r="C8" s="40"/>
+      <c r="D8" s="41" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="39"/>
@@ -3409,17 +3413,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="A9" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="80" t="s">
+      <c r="C9" s="40"/>
+      <c r="D9" s="95" t="s">
         <v>85</v>
       </c>
       <c r="E9" s="39"/>
@@ -3427,15 +3431,15 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="J9" s="42"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="91" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="38" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="41" t="s">
         <v>68</v>
       </c>
       <c r="E10" s="39"/>
@@ -3443,15 +3447,15 @@
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
+      <c r="J10" s="42"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
+      <c r="A11" s="93"/>
+      <c r="B11" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="80" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="95" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="39"/>
@@ -3459,15 +3463,15 @@
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
+      <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="85" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="39"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="38" t="s">
+      <c r="C12" s="40"/>
+      <c r="D12" s="41" t="s">
         <v>91</v>
       </c>
       <c r="E12" s="39"/>
@@ -3475,21 +3479,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="J12" s="42"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="65"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4480,17 +4484,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4499,14 +4500,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4525,19 +4529,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -4549,48 +4553,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
+      <c r="G2" s="71"/>
       <c r="H2" s="96">
         <v>46125</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5947,19 +5951,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5971,48 +5975,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
+      <c r="G2" s="71"/>
+      <c r="H2" s="73">
         <v>46125</v>
       </c>
-      <c r="I2" s="68" t="s">
+      <c r="I2" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7363,19 +7367,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7387,65 +7391,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
+      <c r="G2" s="71"/>
+      <c r="H2" s="73">
         <v>46125</v>
       </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -7456,94 +7460,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -7554,21 +7558,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -7577,11 +7581,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7594,18 +7598,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="49" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="38" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="17" t="s">
         <v>75</v>
       </c>
@@ -7616,84 +7620,84 @@
       <c r="G17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="38"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="50" t="s">
+      <c r="A24" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="39"/>
@@ -7704,21 +7708,21 @@
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
+      <c r="J24" s="42"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="50" t="s">
+      <c r="A25" s="48" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="39"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="38" t="s">
+      <c r="C25" s="40"/>
+      <c r="D25" s="41" t="s">
         <v>78</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
-      <c r="H25" s="42"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="15" t="s">
         <v>26</v>
       </c>
@@ -7727,11 +7731,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="50" t="s">
+      <c r="A26" s="48" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="39"/>
-      <c r="C26" s="42"/>
+      <c r="C26" s="40"/>
       <c r="D26" s="15" t="s">
         <v>28</v>
       </c>
@@ -7744,18 +7748,18 @@
       <c r="G26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="H26" s="49" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="39"/>
-      <c r="J26" s="40"/>
+      <c r="J26" s="42"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41" t="s">
-        <v>73</v>
+      <c r="A27" s="38" t="s">
+        <v>94</v>
       </c>
       <c r="B27" s="39"/>
-      <c r="C27" s="42"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="17" t="s">
         <v>77</v>
       </c>
@@ -7766,83 +7770,83 @@
       <c r="G27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="38" t="s">
+      <c r="H27" s="41" t="s">
         <v>79</v>
       </c>
       <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
+      <c r="J27" s="42"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="41"/>
+      <c r="A28" s="38"/>
       <c r="B28" s="39"/>
-      <c r="C28" s="42"/>
+      <c r="C28" s="40"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="38"/>
+      <c r="H28" s="41"/>
       <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
+      <c r="J28" s="42"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="41"/>
+      <c r="A29" s="38"/>
       <c r="B29" s="39"/>
-      <c r="C29" s="42"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="38"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
+      <c r="J29" s="42"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="41"/>
+      <c r="A30" s="38"/>
       <c r="B30" s="39"/>
-      <c r="C30" s="42"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="38"/>
+      <c r="H30" s="41"/>
       <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
+      <c r="J30" s="42"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="41"/>
+      <c r="A31" s="38"/>
       <c r="B31" s="39"/>
-      <c r="C31" s="42"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="38"/>
+      <c r="H31" s="41"/>
       <c r="I31" s="39"/>
-      <c r="J31" s="40"/>
+      <c r="J31" s="42"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="41"/>
+      <c r="A32" s="38"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="42"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="38"/>
+      <c r="H32" s="41"/>
       <c r="I32" s="39"/>
-      <c r="J32" s="40"/>
+      <c r="J32" s="42"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="47"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="49"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="45"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="65"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="47"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8813,30 +8817,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8853,16 +8843,30 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8885,19 +8889,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8909,65 +8913,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
+      <c r="G2" s="71"/>
+      <c r="H2" s="73">
         <v>46125</v>
       </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -8978,94 +8982,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -9076,21 +9080,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
         <v>86</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -9099,11 +9103,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -9116,18 +9120,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="49" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="38" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="17" t="s">
         <v>87</v>
       </c>
@@ -9138,81 +9142,81 @@
       <c r="G17" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="38"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10183,23 +10187,6 @@
     <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -10214,6 +10201,23 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10236,19 +10240,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
+      <c r="G1" s="56"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -10260,65 +10264,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
+      <c r="G2" s="71"/>
+      <c r="H2" s="73">
         <v>46125</v>
       </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -10329,94 +10333,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
+      <c r="J7" s="61"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="64"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="64"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="64"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="A13" s="62"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="63"/>
+      <c r="J13" s="64"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="48" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -10427,21 +10431,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
+      <c r="J14" s="42"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
         <v>92</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -10450,11 +10454,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
+      <c r="A16" s="48" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -10467,18 +10471,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="59" t="s">
+      <c r="H16" s="49" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="J16" s="42"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="38" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="40"/>
       <c r="D17" s="17" t="s">
         <v>75</v>
       </c>
@@ -10489,83 +10493,83 @@
       <c r="G17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="38" t="s">
+      <c r="H17" s="41" t="s">
         <v>93</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="J17" s="42"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
+      <c r="J18" s="42"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
+      <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="J19" s="42"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
+      <c r="J20" s="42"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
+      <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="J21" s="42"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
+      <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
+      <c r="J22" s="42"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="47"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11536,23 +11540,6 @@
     <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -11567,6 +11554,23 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11586,141 +11590,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="56"/>
+      <c r="Q1" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="56"/>
+      <c r="S1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="52"/>
+      <c r="T1" s="58"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="55"/>
+      <c r="A2" s="62"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="61"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="58"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="64"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="105"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="101"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="79" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="52"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="55"/>
+      <c r="R5" s="55"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="58"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="48" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="38" t="s">
+      <c r="F6" s="40"/>
+      <c r="G6" s="41" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="39"/>
@@ -11735,18 +11739,18 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="40"/>
+      <c r="T6" s="42"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="48" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="38" t="s">
+      <c r="F7" s="40"/>
+      <c r="G7" s="41" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="39"/>
@@ -11761,7 +11765,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="40"/>
+      <c r="T7" s="42"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11960,37 +11964,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="42"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="59" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="59" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="49" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="39"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="59" t="s">
+      <c r="I15" s="40"/>
+      <c r="J15" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="59" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="49" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="39"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="59" t="s">
+      <c r="N15" s="40"/>
+      <c r="O15" s="49" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="39"/>
-      <c r="Q15" s="42"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -12002,37 +12006,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="97">
+      <c r="A16" s="102">
         <v>1</v>
       </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="98" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="98" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="103" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="97" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="39"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="103" t="s">
+      <c r="I16" s="40"/>
+      <c r="J16" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="101" t="s">
+      <c r="K16" s="40"/>
+      <c r="L16" s="99" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="39"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="101" t="s">
+      <c r="N16" s="40"/>
+      <c r="O16" s="99" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="39"/>
-      <c r="Q16" s="42"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12044,37 +12048,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="97">
+      <c r="A17" s="102">
         <v>2</v>
       </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="98" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="98" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="103" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="97" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="39"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="103" t="s">
+      <c r="I17" s="40"/>
+      <c r="J17" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="42"/>
-      <c r="L17" s="101" t="s">
+      <c r="K17" s="40"/>
+      <c r="L17" s="99" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="39"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="101" t="s">
+      <c r="N17" s="40"/>
+      <c r="O17" s="99" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="39"/>
-      <c r="Q17" s="42"/>
+      <c r="Q17" s="40"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12086,23 +12090,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="103"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="97"/>
       <c r="H18" s="39"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="101"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="99"/>
       <c r="M18" s="39"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="101"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="99"/>
       <c r="P18" s="39"/>
-      <c r="Q18" s="42"/>
+      <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12114,23 +12118,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="97"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="103"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="97"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="101"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="99"/>
       <c r="M19" s="39"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="101"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="99"/>
       <c r="P19" s="39"/>
-      <c r="Q19" s="42"/>
+      <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12142,23 +12146,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="97"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="103"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="97"/>
       <c r="H20" s="39"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="101"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="99"/>
       <c r="M20" s="39"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="101"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="99"/>
       <c r="P20" s="39"/>
-      <c r="Q20" s="42"/>
+      <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12170,23 +12174,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="97"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="103"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="97"/>
       <c r="H21" s="39"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="101"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="99"/>
       <c r="M21" s="39"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="101"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="99"/>
       <c r="P21" s="39"/>
-      <c r="Q21" s="42"/>
+      <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12198,23 +12202,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="103"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="97"/>
       <c r="H22" s="39"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="101"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="99"/>
       <c r="M22" s="39"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="101"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="99"/>
       <c r="P22" s="39"/>
-      <c r="Q22" s="42"/>
+      <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12226,23 +12230,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="97"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="103"/>
+      <c r="A23" s="102"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="103"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="97"/>
       <c r="H23" s="39"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="101"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="99"/>
       <c r="M23" s="39"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="101"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="99"/>
       <c r="P23" s="39"/>
-      <c r="Q23" s="42"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12254,23 +12258,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="97"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="103"/>
+      <c r="A24" s="102"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="97"/>
       <c r="H24" s="39"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="101"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="99"/>
       <c r="M24" s="39"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="101"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="99"/>
       <c r="P24" s="39"/>
-      <c r="Q24" s="42"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12282,23 +12286,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="97"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="103"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="97"/>
       <c r="H25" s="39"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="101"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="99"/>
       <c r="M25" s="39"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="101"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="99"/>
       <c r="P25" s="39"/>
-      <c r="Q25" s="42"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12310,23 +12314,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="97"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="103"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="103"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="97"/>
       <c r="H26" s="39"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="101"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="99"/>
       <c r="M26" s="39"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="101"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="99"/>
       <c r="P26" s="39"/>
-      <c r="Q26" s="42"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12338,23 +12342,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="97"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="103"/>
+      <c r="A27" s="102"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="97"/>
       <c r="H27" s="39"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="101"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="99"/>
       <c r="M27" s="39"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="101"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="99"/>
       <c r="P27" s="39"/>
-      <c r="Q27" s="42"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12366,23 +12370,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="103"/>
+      <c r="A28" s="102"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="97"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="101"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="99"/>
       <c r="M28" s="39"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="101"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="99"/>
       <c r="P28" s="39"/>
-      <c r="Q28" s="42"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12394,23 +12398,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="97"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="103"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="103"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="97"/>
       <c r="H29" s="39"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="101"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="97"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="99"/>
       <c r="M29" s="39"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="101"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="99"/>
       <c r="P29" s="39"/>
-      <c r="Q29" s="42"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12422,23 +12426,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="97"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="103"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="97"/>
       <c r="H30" s="39"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="101"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="97"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="99"/>
       <c r="M30" s="39"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="101"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="99"/>
       <c r="P30" s="39"/>
-      <c r="Q30" s="42"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12450,23 +12454,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="99"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="106"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="49"/>
+      <c r="A31" s="105"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="106"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="98"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="100"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="45"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13464,62 +13468,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13544,62 +13548,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D179BB-9EDD-437F-9081-D2BD54C7BFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E27301C-ECA5-4BC3-A60C-78F7048F6635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1357,20 +1357,32 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1381,38 +1393,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1438,19 +1420,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1462,8 +1432,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1480,26 +1480,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1513,7 +1498,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1525,20 +1516,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1546,23 +1552,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1652,22 +1652,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>96863</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>16143</xdr:rowOff>
+      <xdr:colOff>217236</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>150395</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>871778</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>132396</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>265756</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E973320-D031-1D31-4617-FA44C3967B08}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C159F30-1AC1-D3A9-7E64-462619A0CB0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1690,8 +1690,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1113939" y="1081651"/>
-          <a:ext cx="6344619" cy="4475152"/>
+          <a:off x="1269999" y="1086184"/>
+          <a:ext cx="8470625" cy="6032500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2136,67 +2136,67 @@
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2219,14 +2219,14 @@
       <c r="E8" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
@@ -2236,26 +2236,26 @@
       <c r="G13" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="40"/>
+      <c r="H13" s="42"/>
       <c r="I13" s="74" t="s">
         <v>2</v>
       </c>
       <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="K13" s="42"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="74"/>
-      <c r="H14" s="40"/>
+      <c r="H14" s="42"/>
       <c r="I14" s="74"/>
       <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="K14" s="42"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
       <c r="G15" s="74"/>
-      <c r="H15" s="40"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="74"/>
       <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="K15" s="42"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2267,10 +2267,10 @@
       <c r="G17" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="63"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3284,19 +3284,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
@@ -3308,72 +3308,72 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="81">
+      <c r="G2" s="61"/>
+      <c r="H2" s="95">
         <v>46125</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="94" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="87" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="41" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="38" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="39"/>
@@ -3381,15 +3381,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="87" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="38" t="s">
         <v>67</v>
       </c>
       <c r="E7" s="39"/>
@@ -3397,15 +3397,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="42"/>
+      <c r="J7" s="40"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="87" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="41" t="s">
+      <c r="C8" s="42"/>
+      <c r="D8" s="38" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="39"/>
@@ -3413,17 +3413,17 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="42"/>
+      <c r="J8" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="95" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="80" t="s">
         <v>85</v>
       </c>
       <c r="E9" s="39"/>
@@ -3431,15 +3431,15 @@
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="42"/>
+      <c r="J9" s="40"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="84" t="s">
+      <c r="A10" s="89"/>
+      <c r="B10" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="38" t="s">
         <v>68</v>
       </c>
       <c r="E10" s="39"/>
@@ -3447,15 +3447,15 @@
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="42"/>
+      <c r="J10" s="40"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="84" t="s">
+      <c r="A11" s="90"/>
+      <c r="B11" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="95" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="80" t="s">
         <v>83</v>
       </c>
       <c r="E11" s="39"/>
@@ -3463,15 +3463,15 @@
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="42"/>
+      <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="87" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="38" t="s">
         <v>91</v>
       </c>
       <c r="E12" s="39"/>
@@ -3479,21 +3479,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="42"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4484,6 +4484,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4492,25 +4511,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4529,19 +4529,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -4553,48 +4553,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
+      <c r="G2" s="61"/>
       <c r="H2" s="96">
         <v>46125</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5951,19 +5951,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5975,48 +5975,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="73">
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
         <v>46125</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="52"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="92"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7367,19 +7367,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -7391,65 +7391,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="73">
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
         <v>46125</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="52"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -7460,94 +7460,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="64"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="64"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="64"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="64"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="64"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -7558,21 +7558,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="42"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
         <v>80</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -7581,11 +7581,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -7598,18 +7598,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="59" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="42"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
         <v>75</v>
       </c>
@@ -7620,84 +7620,84 @@
       <c r="G17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="38"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="41"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="38"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="41"/>
+      <c r="H19" s="38"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="38"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="41"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="38"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="41"/>
+      <c r="H21" s="38"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="38"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="41"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="48" t="s">
+      <c r="A24" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="39"/>
@@ -7708,21 +7708,21 @@
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
-      <c r="J24" s="42"/>
+      <c r="J24" s="40"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="39"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41" t="s">
+      <c r="C25" s="42"/>
+      <c r="D25" s="38" t="s">
         <v>78</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
-      <c r="H25" s="40"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="15" t="s">
         <v>26</v>
       </c>
@@ -7731,11 +7731,11 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="50" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="39"/>
-      <c r="C26" s="40"/>
+      <c r="C26" s="42"/>
       <c r="D26" s="15" t="s">
         <v>28</v>
       </c>
@@ -7748,18 +7748,18 @@
       <c r="G26" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="59" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="39"/>
-      <c r="J26" s="42"/>
+      <c r="J26" s="40"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="41" t="s">
         <v>94</v>
       </c>
       <c r="B27" s="39"/>
-      <c r="C27" s="40"/>
+      <c r="C27" s="42"/>
       <c r="D27" s="17" t="s">
         <v>77</v>
       </c>
@@ -7770,83 +7770,83 @@
       <c r="G27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I27" s="39"/>
-      <c r="J27" s="42"/>
+      <c r="J27" s="40"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="38"/>
+      <c r="A28" s="41"/>
       <c r="B28" s="39"/>
-      <c r="C28" s="40"/>
+      <c r="C28" s="42"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="18"/>
       <c r="G28" s="18"/>
-      <c r="H28" s="41"/>
+      <c r="H28" s="38"/>
       <c r="I28" s="39"/>
-      <c r="J28" s="42"/>
+      <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="38"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="39"/>
-      <c r="C29" s="40"/>
+      <c r="C29" s="42"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="18"/>
       <c r="G29" s="18"/>
-      <c r="H29" s="41"/>
+      <c r="H29" s="38"/>
       <c r="I29" s="39"/>
-      <c r="J29" s="42"/>
+      <c r="J29" s="40"/>
     </row>
     <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="38"/>
+      <c r="A30" s="41"/>
       <c r="B30" s="39"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="42"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="18"/>
       <c r="G30" s="18"/>
-      <c r="H30" s="41"/>
+      <c r="H30" s="38"/>
       <c r="I30" s="39"/>
-      <c r="J30" s="42"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="38"/>
+      <c r="A31" s="41"/>
       <c r="B31" s="39"/>
-      <c r="C31" s="40"/>
+      <c r="C31" s="42"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="41"/>
+      <c r="H31" s="38"/>
       <c r="I31" s="39"/>
-      <c r="J31" s="42"/>
+      <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="38"/>
+      <c r="A32" s="41"/>
       <c r="B32" s="39"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="42"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="41"/>
+      <c r="H32" s="38"/>
       <c r="I32" s="39"/>
-      <c r="J32" s="42"/>
+      <c r="J32" s="40"/>
     </row>
     <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="43"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="47"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="65"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8817,16 +8817,30 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8843,30 +8857,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8889,19 +8889,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -8913,65 +8913,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="73">
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
         <v>46125</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="52"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -8982,94 +8982,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="64"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="64"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="64"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="64"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="64"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -9080,21 +9080,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="42"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
         <v>86</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -9103,11 +9103,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -9120,18 +9120,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="59" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="42"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
         <v>87</v>
       </c>
@@ -9142,81 +9142,81 @@
       <c r="G17" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="41"/>
+      <c r="H17" s="38"/>
       <c r="I17" s="39"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="38"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="41"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="38"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="41"/>
+      <c r="H19" s="38"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="38"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="41"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="38"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="41"/>
+      <c r="H21" s="38"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="38"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="41"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10187,6 +10187,21 @@
     <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -10203,21 +10218,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10240,19 +10240,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="45"/>
+      <c r="F1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -10264,65 +10264,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="70" t="s">
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="70" t="s">
+      <c r="E2" s="61"/>
+      <c r="F2" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="71"/>
-      <c r="H2" s="73">
+      <c r="G2" s="61"/>
+      <c r="H2" s="66">
         <v>46125</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="52"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="69"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="57" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="58"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="50" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="39"/>
@@ -10333,94 +10333,94 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="42"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="61"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="64"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="64"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="58"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="64"/>
+      <c r="A11" s="56"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="64"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="58"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="64"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="58"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="50" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="39"/>
@@ -10431,21 +10431,21 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="42"/>
+      <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="38" t="s">
         <v>92</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="H15" s="42"/>
       <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
@@ -10454,11 +10454,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="50" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="15" t="s">
         <v>28</v>
       </c>
@@ -10471,18 +10471,18 @@
       <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="59" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="42"/>
+      <c r="J16" s="40"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="17" t="s">
         <v>75</v>
       </c>
@@ -10493,83 +10493,83 @@
       <c r="G17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="38" t="s">
         <v>93</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="42"/>
+      <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="38"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
+      <c r="C18" s="42"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="41"/>
+      <c r="H18" s="38"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="42"/>
+      <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="38"/>
+      <c r="A19" s="41"/>
       <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
+      <c r="C19" s="42"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="41"/>
+      <c r="H19" s="38"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="42"/>
+      <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="38"/>
+      <c r="A20" s="41"/>
       <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="41"/>
+      <c r="H20" s="38"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="42"/>
+      <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="38"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="41"/>
+      <c r="H21" s="38"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="42"/>
+      <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="38"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="42"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="41"/>
+      <c r="H22" s="38"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="42"/>
+      <c r="J22" s="40"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="47"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11540,6 +11540,21 @@
     <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -11556,21 +11571,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11590,141 +11590,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="69" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="69" t="s">
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="69" t="s">
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="69" t="s">
+      <c r="P1" s="45"/>
+      <c r="Q1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="69" t="s">
+      <c r="R1" s="45"/>
+      <c r="S1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="58"/>
+      <c r="T1" s="52"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="61"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="60"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="55"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="64"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="58"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="80"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="101"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="85"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="85"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="85"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="105"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="94" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="58"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="44"/>
+      <c r="T5" s="52"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="50" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="38" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="39"/>
@@ -11739,18 +11739,18 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="42"/>
+      <c r="T6" s="40"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="50" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41" t="s">
+      <c r="F7" s="42"/>
+      <c r="G7" s="38" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="39"/>
@@ -11765,7 +11765,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="42"/>
+      <c r="T7" s="40"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11964,37 +11964,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="42"/>
       <c r="C15" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="49" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="49" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="59" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="49" t="s">
+      <c r="I15" s="42"/>
+      <c r="J15" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="49" t="s">
+      <c r="K15" s="42"/>
+      <c r="L15" s="59" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="49" t="s">
+      <c r="N15" s="42"/>
+      <c r="O15" s="59" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="Q15" s="42"/>
       <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
@@ -12006,37 +12006,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="102">
+      <c r="A16" s="97">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="103" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="103" t="s">
+      <c r="D16" s="42"/>
+      <c r="E16" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="97" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="103" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="97" t="s">
+      <c r="I16" s="42"/>
+      <c r="J16" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="99" t="s">
+      <c r="K16" s="42"/>
+      <c r="L16" s="101" t="s">
         <v>57</v>
       </c>
       <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="99" t="s">
+      <c r="N16" s="42"/>
+      <c r="O16" s="101" t="s">
         <v>58</v>
       </c>
       <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="Q16" s="42"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -12048,37 +12048,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="102">
+      <c r="A17" s="97">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="103" t="s">
+      <c r="B17" s="42"/>
+      <c r="C17" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="103" t="s">
+      <c r="D17" s="42"/>
+      <c r="E17" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="97" t="s">
+      <c r="F17" s="42"/>
+      <c r="G17" s="103" t="s">
         <v>61</v>
       </c>
       <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="97" t="s">
+      <c r="I17" s="42"/>
+      <c r="J17" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="99" t="s">
+      <c r="K17" s="42"/>
+      <c r="L17" s="101" t="s">
         <v>63</v>
       </c>
       <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="99" t="s">
+      <c r="N17" s="42"/>
+      <c r="O17" s="101" t="s">
         <v>64</v>
       </c>
       <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="Q17" s="42"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -12090,23 +12090,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="97"/>
+      <c r="A18" s="97"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="103"/>
       <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="99"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="101"/>
       <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="99"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="101"/>
       <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
+      <c r="Q18" s="42"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -12118,23 +12118,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="97"/>
+      <c r="A19" s="97"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="103"/>
       <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="99"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="103"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="101"/>
       <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="99"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="101"/>
       <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="Q19" s="42"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -12146,23 +12146,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="103"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="97"/>
+      <c r="A20" s="97"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="103"/>
       <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="99"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="101"/>
       <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="99"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="101"/>
       <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
+      <c r="Q20" s="42"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -12174,23 +12174,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="97"/>
+      <c r="A21" s="97"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="103"/>
       <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="99"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="101"/>
       <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="99"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="101"/>
       <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="Q21" s="42"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -12202,23 +12202,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="97"/>
+      <c r="A22" s="97"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="98"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="103"/>
       <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="97"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="99"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="101"/>
       <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="99"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="101"/>
       <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -12230,23 +12230,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="103"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="97"/>
+      <c r="A23" s="97"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="103"/>
       <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="99"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="103"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="101"/>
       <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="99"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="101"/>
       <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="Q23" s="42"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -12258,23 +12258,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="97"/>
+      <c r="A24" s="97"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="103"/>
       <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="99"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="101"/>
       <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="99"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="101"/>
       <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="Q24" s="42"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -12286,23 +12286,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="97"/>
+      <c r="A25" s="97"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="97"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="99"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="103"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="101"/>
       <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="99"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="101"/>
       <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="Q25" s="42"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -12314,23 +12314,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="103"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="97"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="103"/>
       <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="97"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="99"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="101"/>
       <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="99"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="101"/>
       <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="Q26" s="42"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -12342,23 +12342,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="97"/>
+      <c r="A27" s="97"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="103"/>
       <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="97"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="99"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="103"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="101"/>
       <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="99"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="101"/>
       <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="Q27" s="42"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -12370,23 +12370,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="97"/>
+      <c r="A28" s="97"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="103"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="99"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="103"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="101"/>
       <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="99"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="101"/>
       <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="Q28" s="42"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -12398,23 +12398,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="97"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="103"/>
       <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="97"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="99"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="101"/>
       <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="99"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="101"/>
       <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="Q29" s="42"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -12426,23 +12426,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="97"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="103"/>
       <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="97"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="99"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="103"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="101"/>
       <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="99"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="101"/>
       <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="Q30" s="42"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -12454,23 +12454,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="105"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="106"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="45"/>
-      <c r="O31" s="100"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="45"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="102"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="49"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -13468,6 +13468,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -13492,118 +13604,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCに貼ってある番号\Documents\project\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E27301C-ECA5-4BC3-A60C-78F7048F6635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63AAC62-C71D-4C3F-8328-7D8B752AE5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="45" windowWidth="15135" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
-    <sheet name="画面設計書 (2)" sheetId="7" r:id="rId6"/>
-    <sheet name="画面設計書 (3)" sheetId="8" r:id="rId7"/>
+    <sheet name="画面設計書 (タスク削除完了画面)" sheetId="7" r:id="rId6"/>
+    <sheet name="画面設計書 (タスク削除エラー画面)" sheetId="8" r:id="rId7"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
@@ -27,15 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -249,38 +246,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>なし</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>GET</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスクを削除する</t>
-    <rPh sb="4" eb="6">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>登録されたタスクを削除する</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ユーザーがシステムにログインしていること</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -292,21 +258,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>戻る</t>
-    <rPh sb="0" eb="1">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>POST</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>削除</t>
-    <rPh sb="0" eb="2">
-      <t>サクジョ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -314,17 +266,6 @@
     <rPh sb="7" eb="9">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>TaskDeketeServletへ遷移</t>
-    <rPh sb="18" eb="20">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>task-detail.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -342,93 +283,11 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">3a1.ユーザーが「タスク削除確認」画面の「戻る」を選択する
-3a2.システムが「タスク詳細」画面を表示する
-4a．タスクの削除に失敗した場合、システムが「エラー画面」を表示する
-</t>
-    <rPh sb="22" eb="23">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="85" eb="87">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>TaskManager62システム</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t xml:space="preserve">1．ユーザーがタスク詳細画面のタスク削除を選択する
-2．システムがタスク削除確認画面を表示する
-3．ユーザーがタスクの削除を確定する
-4．タスクの削除に成功した場合、システムがタスク削除完了画面を表示する
-</t>
-    <rPh sb="10" eb="12">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="62" eb="64">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="98" eb="100">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>メニュー</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -462,34 +321,157 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>システムはDB上から該当タスクを削除すること</t>
-    <rPh sb="7" eb="8">
-      <t>ジョウ</t>
+    <t>task-delete-confirm.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>②</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクを削除する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムに登録されたタスクを選択して削除する</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
     </rPh>
-    <rPh sb="10" eb="12">
-      <t>ガイトウ</t>
+    <rPh sb="14" eb="16">
+      <t>センタク</t>
     </rPh>
-    <rPh sb="16" eb="18">
+    <rPh sb="18" eb="20">
       <t>サクジョ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-delete-confirm.jsp</t>
+    <t>3a1.ユーザーがタスクの削除を中止し、直前の画面に戻る
+3a2.システムがタスク詳細画面を表示する</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク削除確認画面に遷移</t>
-    <rPh sb="3" eb="9">
-      <t>サクジョカクニンガメン</t>
+    <t>1．ユーザーがタスク詳細画面でタスクの削除を選択する
+2．システムがタスク削除確認画面を表示する
+3．ユーザーがタスクの削除を確定する
+4．システムがタスク削除完了画面を表示する</t>
+    <rPh sb="10" eb="12">
+      <t>ショウサイ</t>
     </rPh>
-    <rPh sb="10" eb="12">
-      <t>センイ</t>
+    <rPh sb="12" eb="14">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>②</t>
+    <t>ユーザーがシステムにログインしていること
+対象のタスクがデータベースに存在していること</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>4a．対象のタスクがデータベースに存在しない場合
+4a1.システムがタスク削除エラー画面を表示する</t>
+    <rPh sb="3" eb="5">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象のタスクがデータベースから削除されていること</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>フォーム定義</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除画面へ</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除画面へ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>削除する</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>詳細画面へ</t>
+    <rPh sb="0" eb="4">
+      <t>ショウサイガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-detaile.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名 62期</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -497,10 +479,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
+    <numFmt numFmtId="177" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -561,6 +544,13 @@
       <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1242,7 +1232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1293,12 +1283,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1357,6 +1341,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1366,49 +1374,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1417,10 +1398,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1432,37 +1464,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1480,58 +1491,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1585,23 +1578,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>102054</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>148116</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>992028</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>150801</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>34848</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>4029</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A594E3AB-DF04-620F-4544-7A2EE003AE7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55B4689F-1FE5-003D-1242-8B76B841A5EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1624,8 +1617,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1122590" y="1032580"/>
-          <a:ext cx="6502920" cy="4765185"/>
+          <a:off x="0" y="1836965"/>
+          <a:ext cx="8865884" cy="2684635"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1651,23 +1644,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>217236</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>166255</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>150395</xdr:rowOff>
+      <xdr:rowOff>146464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>265756</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>86591</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>12125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C159F30-1AC1-D3A9-7E64-462619A0CB0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15645FDC-E67C-D634-86C6-CE76769F878B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1690,8 +1683,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1269999" y="1086184"/>
-          <a:ext cx="8470625" cy="6032500"/>
+          <a:off x="512619" y="1047009"/>
+          <a:ext cx="7263245" cy="4073980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1718,22 +1711,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1081848</xdr:colOff>
+      <xdr:colOff>818326</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>40374</xdr:rowOff>
+      <xdr:rowOff>56427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>823850</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>978745</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>194661</xdr:rowOff>
+      <xdr:rowOff>34763</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24C90233-EB62-8BE8-1639-834EBF600A2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B35101C0-16D3-E9C0-2F09-E96A8035B704}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1756,8 +1749,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3231295" y="1582918"/>
-          <a:ext cx="3079967" cy="1772694"/>
+          <a:off x="2969855" y="1580427"/>
+          <a:ext cx="2379184" cy="1591983"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1783,23 +1776,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>820772</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>30399</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>91197</xdr:rowOff>
+      <xdr:rowOff>121594</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>405319</xdr:colOff>
+      <xdr:colOff>182394</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>145482</xdr:rowOff>
+      <xdr:rowOff>139277</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB7C19F9-BA0A-1FC5-B0DB-423696209143}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B329F8DD-1BE9-5C9C-7063-8780B3E1120D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1822,8 +1815,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2968963" y="1651676"/>
-          <a:ext cx="2928430" cy="1635029"/>
+          <a:off x="3293218" y="1682073"/>
+          <a:ext cx="2381250" cy="1598427"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1850,22 +1843,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>694532</xdr:colOff>
+      <xdr:colOff>1041798</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>148827</xdr:rowOff>
+      <xdr:rowOff>109141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>492658</xdr:colOff>
+      <xdr:colOff>109141</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>228203</xdr:rowOff>
+      <xdr:rowOff>145768</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{694432C0-FCC8-88A0-8340-A95E930A29E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9192BCC1-ED33-87AC-E60B-627BAF09517A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1888,8 +1881,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2847579" y="1686718"/>
-          <a:ext cx="3131876" cy="1686719"/>
+          <a:off x="3194845" y="1647032"/>
+          <a:ext cx="2401093" cy="1643970"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2118,85 +2111,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2216,46 +2209,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="57"/>
-      <c r="K8" s="57"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="57"/>
+      <c r="E8" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="74" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="42"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="86">
+        <v>46127</v>
+      </c>
+      <c r="J13" s="45"/>
+      <c r="K13" s="62"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="74"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="42"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="62"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="74"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="42"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="62"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2264,13 +2257,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
+      <c r="G17" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3284,216 +3277,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="70"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="59" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="95">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="69"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
+    </row>
+    <row r="8" spans="1:10" ht="32.25" customHeight="1">
+      <c r="A8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
+      <c r="B8" s="45"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="88" t="s">
+      <c r="B9" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="C9" s="62"/>
+      <c r="D9" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="64"/>
+      <c r="B10" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="89"/>
-      <c r="B10" s="91" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="46"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="90"/>
-      <c r="B11" s="91" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="46"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="B12" s="45"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="46"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="81" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="48"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="49"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="65"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4529,72 +4522,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="A1" s="87" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="78">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="96">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -4829,7 +4822,6 @@
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
@@ -5951,72 +5943,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
+      <c r="A1" s="87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="88">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="70"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="93"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="72"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6179,7 +6171,6 @@
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
@@ -7358,7 +7349,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J988"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7367,1857 +7358,345 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="88">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="70"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="93"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="96"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="96"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="96"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="96"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="96"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="96"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="15" t="s">
+      <c r="J15" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
+      <c r="A18" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="A19" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
+      <c r="A20" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="46"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A21" s="89" t="s">
+        <v>80</v>
+      </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>69</v>
+      </c>
       <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+      <c r="G21" s="18" t="s">
+        <v>92</v>
+      </c>
       <c r="H21" s="38"/>
       <c r="I21" s="39"/>
       <c r="J21" s="40"/>
     </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="40"/>
-    </row>
-    <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="I27" s="39"/>
-      <c r="J27" s="40"/>
-    </row>
-    <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="41"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
-    </row>
-    <row r="29" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="42"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
-    </row>
-    <row r="30" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39"/>
-      <c r="J30" s="40"/>
-    </row>
-    <row r="31" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A31" s="41"/>
-      <c r="B31" s="39"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="40"/>
-    </row>
-    <row r="32" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="40"/>
-    </row>
-    <row r="33" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A33" s="47"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="65"/>
-    </row>
-    <row r="34" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="37" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="38" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="39" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="40" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="41" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="42" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="43" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="45" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="46" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="47" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="48" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E1A6AD-24AE-4696-B2EE-8A4E4C481296}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J990"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="3" width="5.140625" customWidth="1"/>
-    <col min="4" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
-    </row>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10183,41 +8662,34 @@
     <row r="986" ht="12.75" customHeight="1"/>
     <row r="987" ht="12.75" customHeight="1"/>
     <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
+  <mergeCells count="26">
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10226,12 +8698,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAAFCE6-8E67-44F1-B2B1-1F1D486C557E}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E1A6AD-24AE-4696-B2EE-8A4E4C481296}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J990"/>
+  <dimension ref="A1:J984"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -10240,337 +8712,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="88">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="70"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="45"/>
-      <c r="F1" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="45"/>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="66">
-        <v>46125</v>
-      </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="69"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="70"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="70"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="92" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="52"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="A7" s="93"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="58"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="96"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="56"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="58"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="58"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="96"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="56"/>
-      <c r="B11" s="57"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="58"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="96"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="58"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="96"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="56"/>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="91" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="B15" s="45"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="15" t="s">
+      <c r="J15" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="91" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="B16" s="45"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="38" t="s">
-        <v>93</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="H17" s="38"/>
       <c r="I17" s="39"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="40"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="39"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="40"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="47"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="65"/>
-    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11532,36 +9938,14 @@
     <row r="982" ht="12.75" customHeight="1"/>
     <row r="983" ht="12.75" customHeight="1"/>
     <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="D15:H15"/>
+  <mergeCells count="19">
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11569,8 +9953,1279 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAAFCE6-8E67-44F1-B2B1-1F1D486C557E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J984"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="5.140625" customWidth="1"/>
+    <col min="4" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" customHeight="1">
+      <c r="A1" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="60"/>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="60"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="75"/>
+      <c r="F2" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="75"/>
+      <c r="H2" s="88">
+        <v>46125</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="70"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="71"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="92" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="93"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="95"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="96"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="96"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="96"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="96"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="96"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="96"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="46"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="45"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="46"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="36"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="33" ht="12.75" customHeight="1"/>
+    <row r="34" ht="12.75" customHeight="1"/>
+    <row r="35" ht="12.75" customHeight="1"/>
+    <row r="36" ht="12.75" customHeight="1"/>
+    <row r="37" ht="12.75" customHeight="1"/>
+    <row r="38" ht="12.75" customHeight="1"/>
+    <row r="39" ht="12.75" customHeight="1"/>
+    <row r="40" ht="12.75" customHeight="1"/>
+    <row r="41" ht="12.75" customHeight="1"/>
+    <row r="42" ht="12.75" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="47" ht="12.75" customHeight="1"/>
+    <row r="48" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11590,182 +11245,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="42"/>
+      <c r="M1" s="42"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="73" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="60"/>
+      <c r="S1" s="73" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="43"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="95"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="53"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="96"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="106"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="45"/>
-      <c r="S1" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="52"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="55"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="62"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="62"/>
-      <c r="T3" s="58"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="85"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="105"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="79" t="s">
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="43"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="52"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="45"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="46"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="40"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="40"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="45"/>
+      <c r="S7" s="45"/>
+      <c r="T7" s="46"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11790,156 +11445,156 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-    </row>
-    <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-    </row>
-    <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-    </row>
-    <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
+      <c r="F12" s="20"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-    </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
       <c r="A14" s="8"/>
@@ -11964,522 +11619,522 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="105" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="62"/>
+      <c r="E15" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="104" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="59" t="s">
+      <c r="F15" s="62"/>
+      <c r="G15" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="59" t="s">
+      <c r="H15" s="45"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="59" t="s">
+      <c r="K15" s="62"/>
+      <c r="L15" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="42"/>
-      <c r="L15" s="59" t="s">
+      <c r="M15" s="45"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="59" t="s">
+      <c r="P15" s="45"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="98">
+        <v>1</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="99" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="97">
-        <v>1</v>
-      </c>
-      <c r="B16" s="42"/>
-      <c r="C16" s="98" t="s">
+      <c r="D16" s="62"/>
+      <c r="E16" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="98" t="s">
+      <c r="F16" s="62"/>
+      <c r="G16" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="103" t="s">
+      <c r="H16" s="45"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="103" t="s">
+      <c r="K16" s="62"/>
+      <c r="L16" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="42"/>
-      <c r="L16" s="101" t="s">
+      <c r="M16" s="45"/>
+      <c r="N16" s="62"/>
+      <c r="O16" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="101" t="s">
+      <c r="P16" s="45"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+    </row>
+    <row r="17" spans="1:26" ht="41.25" customHeight="1">
+      <c r="A17" s="98">
+        <v>2</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-    </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="97">
-        <v>2</v>
-      </c>
-      <c r="B17" s="42"/>
-      <c r="C17" s="98" t="s">
+      <c r="D17" s="62"/>
+      <c r="E17" s="99" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="98" t="s">
+      <c r="F17" s="62"/>
+      <c r="G17" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="103" t="s">
+      <c r="H17" s="45"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="103" t="s">
+      <c r="K17" s="62"/>
+      <c r="L17" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="K17" s="42"/>
-      <c r="L17" s="101" t="s">
+      <c r="M17" s="45"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="97"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="101"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="A18" s="98"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="62"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="97"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="103"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="101"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="A19" s="98"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="104"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="102"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="97"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="101"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="A20" s="98"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="104"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="97"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="103"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="102"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="102"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="97"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="101"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="A22" s="98"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="104"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="102"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="102"/>
+      <c r="P22" s="45"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="97"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="98"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="103"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="101"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="A23" s="98"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="104"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="102"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="97"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="A24" s="98"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="62"/>
+      <c r="O24" s="102"/>
+      <c r="P24" s="45"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="97"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="103"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="103"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="A25" s="98"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="104"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="104"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="97"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="103"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="103"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="101"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="101"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="A26" s="98"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="104"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="97"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="103"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="101"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="A27" s="98"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="97"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="103"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="101"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="101"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="A28" s="98"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="62"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="97"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="98"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="103"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="101"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="101"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="97"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="103"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="101"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="101"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="A30" s="98"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="99"/>
+      <c r="A31" s="100"/>
       <c r="B31" s="49"/>
-      <c r="C31" s="100"/>
+      <c r="C31" s="101"/>
       <c r="D31" s="49"/>
-      <c r="E31" s="100"/>
+      <c r="E31" s="101"/>
       <c r="F31" s="49"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="48"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="39"/>
       <c r="I31" s="49"/>
-      <c r="J31" s="106"/>
+      <c r="J31" s="107"/>
       <c r="K31" s="49"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="48"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="39"/>
       <c r="N31" s="49"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="48"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="39"/>
       <c r="Q31" s="49"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="3"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63AAC62-C71D-4C3F-8328-7D8B752AE5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3431C9-974B-4C66-A7CB-BC643DEEBD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="45" windowWidth="15135" windowHeight="7665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -461,10 +461,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-detaile.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>チーム名 62期</t>
     <rPh sb="3" eb="4">
       <t>メイ</t>
@@ -472,6 +468,10 @@
     <rPh sb="7" eb="8">
       <t>キ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-detail.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1347,92 +1347,65 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1452,47 +1425,74 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1500,13 +1500,16 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1524,8 +1527,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1533,29 +1548,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1644,23 +1644,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>166255</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>146464</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>337038</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76234</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>86591</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>12125</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>959826</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>148004</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15645FDC-E67C-D634-86C6-CE76769F878B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE7FCC05-2E33-DCD3-A675-19D382C58403}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1683,8 +1683,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="512619" y="1047009"/>
-          <a:ext cx="7263245" cy="4073980"/>
+          <a:off x="1025769" y="1307157"/>
+          <a:ext cx="6535615" cy="3779193"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2111,85 +2111,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="83" t="s">
+      <c r="C2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2209,46 +2209,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="81" t="s">
+      <c r="G13" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="62"/>
-      <c r="I13" s="86">
+      <c r="H13" s="40"/>
+      <c r="I13" s="46">
         <v>46127</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="81"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="62"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="40"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="81"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="62"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2257,13 +2257,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="G17" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3277,19 +3277,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3301,192 +3301,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="44" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="61" t="s">
+      <c r="A7" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="44" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="40"/>
+      <c r="D9" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="67"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="64"/>
-      <c r="B10" s="66" t="s">
+      <c r="A10" s="80"/>
+      <c r="B10" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="47" t="s">
+      <c r="C10" s="40"/>
+      <c r="D10" s="86" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="46"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66" t="s">
+      <c r="A11" s="81"/>
+      <c r="B11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="46"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="61" t="s">
+      <c r="A12" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="44" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="48" t="s">
+      <c r="A13" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="83"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4477,17 +4477,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4496,14 +4493,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4525,16 +4525,16 @@
       <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4546,48 +4546,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="78">
+      <c r="G2" s="50"/>
+      <c r="H2" s="55">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5946,16 +5946,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -5967,48 +5967,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="72"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6279,7 +6279,6 @@
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -7361,16 +7360,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7382,190 +7381,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="92" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="44" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
@@ -7574,11 +7573,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -7591,18 +7590,18 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="97" t="s">
+      <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="49"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="17" t="s">
         <v>91</v>
       </c>
@@ -7613,37 +7612,37 @@
       <c r="G17" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="83"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="46"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="91" t="s">
+      <c r="A19" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="45"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="62"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="15" t="s">
         <v>25</v>
       </c>
@@ -7652,11 +7651,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="45"/>
-      <c r="C20" s="62"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
       <c r="D20" s="15" t="s">
         <v>27</v>
       </c>
@@ -7669,18 +7668,18 @@
       <c r="G20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="97" t="s">
+      <c r="H20" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="91" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="49"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="17" t="s">
         <v>92</v>
       </c>
@@ -7691,9 +7690,9 @@
       <c r="G21" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
+      <c r="H21" s="82"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="83"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8664,6 +8663,16 @@
     <row r="988" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:J20"/>
     <mergeCell ref="A21:C21"/>
@@ -8680,16 +8689,6 @@
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8715,16 +8714,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8736,190 +8735,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="92" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="93" t="s">
         <v>77</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="89" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="44" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
@@ -8928,11 +8927,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -8945,18 +8944,18 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="97" t="s">
+      <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="49"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="37" t="s">
         <v>76</v>
       </c>
@@ -8967,9 +8966,9 @@
       <c r="G17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="83"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9940,12 +9939,6 @@
     <row r="984" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -9958,6 +9951,12 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
@@ -9984,16 +9983,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="73" t="s">
+      <c r="E1" s="48"/>
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="60"/>
+      <c r="G1" s="48"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10005,190 +10004,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="74" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="75"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="70"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="71"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="62"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="71"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="92" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="93" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="96"/>
+      <c r="A8" s="74"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="96"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="96"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="96"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="96"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="96"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="46"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="44" t="s">
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
@@ -10197,11 +10196,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="45"/>
-      <c r="C16" s="62"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -10214,18 +10213,18 @@
       <c r="G16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="97" t="s">
+      <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="45"/>
-      <c r="J16" s="46"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="49"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="17" t="s">
         <v>89</v>
       </c>
@@ -10234,9 +10233,9 @@
       <c r="G17" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="40"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="83"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11207,12 +11206,6 @@
     <row r="984" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D1:E1"/>
@@ -11225,6 +11218,12 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
@@ -11245,182 +11244,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="73" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="73" t="s">
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="73" t="s">
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="73" t="s">
+      <c r="P1" s="48"/>
+      <c r="Q1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="60"/>
-      <c r="S1" s="73" t="s">
+      <c r="R1" s="48"/>
+      <c r="S1" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="43"/>
+      <c r="T1" s="85"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="75"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="95"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="96"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="76"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="76"/>
-      <c r="T3" s="96"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="97"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="56"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="106"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="102"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="41" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="43"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="78"/>
+      <c r="O5" s="78"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="78"/>
+      <c r="R5" s="78"/>
+      <c r="S5" s="78"/>
+      <c r="T5" s="85"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="44" t="s">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="45"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="46"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="67"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="44" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
-      <c r="S7" s="45"/>
-      <c r="T7" s="46"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="67"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11619,37 +11618,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="62"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="97" t="s">
+      <c r="D15" s="40"/>
+      <c r="E15" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="97" t="s">
+      <c r="F15" s="40"/>
+      <c r="G15" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="97" t="s">
+      <c r="H15" s="39"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="62"/>
-      <c r="L15" s="97" t="s">
+      <c r="K15" s="40"/>
+      <c r="L15" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="45"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="97" t="s">
+      <c r="M15" s="39"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="40"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -11661,37 +11660,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="98">
+      <c r="A16" s="103">
         <v>1</v>
       </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="99" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="99" t="s">
+      <c r="D16" s="40"/>
+      <c r="E16" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="104" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="104" t="s">
+      <c r="H16" s="39"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="62"/>
-      <c r="L16" s="102" t="s">
+      <c r="K16" s="40"/>
+      <c r="L16" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="45"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="102" t="s">
+      <c r="M16" s="39"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -11703,37 +11702,37 @@
       <c r="Z16" s="33"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="98">
+      <c r="A17" s="103">
         <v>2</v>
       </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="99" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="104" t="s">
+      <c r="F17" s="40"/>
+      <c r="G17" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="45"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="104" t="s">
+      <c r="H17" s="39"/>
+      <c r="I17" s="40"/>
+      <c r="J17" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="62"/>
-      <c r="L17" s="102" t="s">
+      <c r="K17" s="40"/>
+      <c r="L17" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="45"/>
-      <c r="N17" s="62"/>
-      <c r="O17" s="102" t="s">
+      <c r="M17" s="39"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="45"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -11745,23 +11744,23 @@
       <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="45"/>
-      <c r="Q18" s="62"/>
+      <c r="A18" s="103"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -11773,23 +11772,23 @@
       <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="98"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="45"/>
-      <c r="Q19" s="62"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -11801,23 +11800,23 @@
       <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="98"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="62"/>
+      <c r="A20" s="103"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -11829,23 +11828,23 @@
       <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="98"/>
-      <c r="B21" s="62"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="62"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -11857,23 +11856,23 @@
       <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="98"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="45"/>
-      <c r="Q22" s="62"/>
+      <c r="A22" s="103"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -11885,23 +11884,23 @@
       <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="98"/>
-      <c r="B23" s="62"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="62"/>
+      <c r="A23" s="103"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -11913,23 +11912,23 @@
       <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="98"/>
-      <c r="B24" s="62"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="62"/>
+      <c r="A24" s="103"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -11941,23 +11940,23 @@
       <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="98"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="45"/>
-      <c r="Q25" s="62"/>
+      <c r="A25" s="103"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="40"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -11969,23 +11968,23 @@
       <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="98"/>
-      <c r="B26" s="62"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="45"/>
-      <c r="Q26" s="62"/>
+      <c r="A26" s="103"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="98"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="40"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -11997,23 +11996,23 @@
       <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="98"/>
-      <c r="B27" s="62"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="45"/>
-      <c r="Q27" s="62"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="40"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="39"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="39"/>
+      <c r="Q27" s="40"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -12025,23 +12024,23 @@
       <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="98"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="62"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="62"/>
+      <c r="A28" s="103"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="100"/>
+      <c r="P28" s="39"/>
+      <c r="Q28" s="40"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -12053,23 +12052,23 @@
       <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="98"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="62"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="62"/>
+      <c r="A29" s="103"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="40"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -12081,23 +12080,23 @@
       <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="98"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="62"/>
+      <c r="A30" s="103"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="39"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="39"/>
+      <c r="Q30" s="40"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -12109,23 +12108,23 @@
       <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="100"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="39"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="39"/>
-      <c r="Q31" s="49"/>
+      <c r="A31" s="106"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="69"/>
+      <c r="N31" s="70"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="70"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
@@ -13123,62 +13122,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -13203,62 +13202,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_タスク削除機能.xlsx
+++ b/document/成果物ドキュメント_タスク削除機能.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3431C9-974B-4C66-A7CB-BC643DEEBD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069EDB6B-AD37-442F-8912-7CD9D8A59230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,16 +236,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>商品企画部の従業員</t>
-    <rPh sb="0" eb="5">
-      <t>ショウヒンキカクブ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>GET</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -391,23 +381,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザーがシステムにログインしていること
-対象のタスクがデータベースに存在していること</t>
-    <rPh sb="0" eb="2">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>タイショウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>4a．対象のタスクがデータベースに存在しない場合
 4a1.システムがタスク削除エラー画面を表示する</t>
     <rPh sb="3" eb="5">
@@ -472,6 +445,36 @@
   </si>
   <si>
     <t>task-detail.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>対象のタスクがシステムに存在すること
+対象のタスクの担当者と同一のユーザーがシステムにログインしていること</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ドウイツ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>商品企画部の従業員(ユーザー)</t>
+    <rPh sb="0" eb="5">
+      <t>ショウヒンキカクブ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ジュウギョウイン</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1347,33 +1350,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1428,8 +1404,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1456,6 +1438,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1493,6 +1478,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2111,85 +2114,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2209,46 +2212,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="E8" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="46">
+      <c r="H13" s="56"/>
+      <c r="I13" s="86">
         <v>46127</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="56"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="56"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="56"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2257,13 +2260,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="G17" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3277,19 +3280,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -3301,192 +3304,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="58"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="85"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="66" t="s">
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="58"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="60"/>
+    </row>
+    <row r="8" spans="1:10" ht="32.25" customHeight="1">
+      <c r="A8" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="58"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="80" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="60"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="60"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="74"/>
+      <c r="B10" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="67"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="65" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="67"/>
-    </row>
-    <row r="8" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A8" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="86" t="s">
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="60"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="75"/>
+      <c r="B11" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="60"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="58"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="67"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="86" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="67"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="80"/>
-      <c r="B10" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="86" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="67"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="81"/>
-      <c r="B11" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="86" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="67"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="67"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="68" t="s">
+      <c r="A13" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="83"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="76"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="77"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4525,16 +4528,16 @@
       <c r="A1" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -4546,48 +4549,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="55">
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
+      <c r="H2" s="46">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5946,16 +5949,16 @@
       <c r="A1" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -5967,48 +5970,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="63"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7360,16 +7363,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7381,78 +7384,78 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="48"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="93" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="94"/>
@@ -7467,117 +7470,117 @@
       <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="74"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="74"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
       <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="74"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="74"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
       <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -7593,69 +7596,69 @@
       <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A17" s="91" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>69</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="83"/>
+        <v>89</v>
+      </c>
+      <c r="H17" s="76"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="77"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="67"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="60"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="40"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="56"/>
       <c r="I19" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="15" t="s">
         <v>27</v>
       </c>
@@ -7671,28 +7674,28 @@
       <c r="H20" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="67"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="60"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A21" s="91" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="69"/>
-      <c r="C21" s="70"/>
+        <v>79</v>
+      </c>
+      <c r="B21" s="62"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="82"/>
-      <c r="I21" s="69"/>
-      <c r="J21" s="83"/>
+        <v>90</v>
+      </c>
+      <c r="H21" s="76"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="77"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8714,16 +8717,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8735,78 +8738,78 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="48"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="93" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="85"/>
+        <v>76</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="94"/>
@@ -8821,117 +8824,117 @@
       <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="74"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="74"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
       <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="74"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="74"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
       <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="67"/>
+        <v>86</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -8947,28 +8950,28 @@
       <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A17" s="91" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>69</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="83"/>
+        <v>75</v>
+      </c>
+      <c r="H17" s="76"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="77"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9983,16 +9986,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="47" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="48"/>
+      <c r="G1" s="39"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -10004,78 +10007,78 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="50"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="41"/>
       <c r="H2" s="88">
         <v>46125</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="62"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="74"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="62"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
       <c r="A5" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="48"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="93" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="85"/>
+        <v>77</v>
+      </c>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="94"/>
@@ -10090,117 +10093,117 @@
       <c r="J7" s="96"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="74"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="74"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
       <c r="J9" s="97"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="74"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
       <c r="J10" s="97"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
       <c r="J11" s="97"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="74"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
       <c r="J12" s="97"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="74"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
       <c r="J13" s="97"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
       <c r="A14" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="60"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
       <c r="A15" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="66" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
       <c r="A16" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="56"/>
       <c r="D16" s="15" t="s">
         <v>27</v>
       </c>
@@ -10216,26 +10219,26 @@
       <c r="H16" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="39"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
       <c r="A17" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
+        <v>67</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="63"/>
       <c r="D17" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E17" s="36"/>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="83"/>
+        <v>88</v>
+      </c>
+      <c r="H17" s="76"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="77"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11244,182 +11247,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="64" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="47" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="47" t="s">
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="47" t="s">
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="47" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="47" t="s">
+      <c r="R1" s="39"/>
+      <c r="S1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="85"/>
+      <c r="T1" s="79"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="74"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="49"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="40"/>
       <c r="H2" s="95"/>
       <c r="I2" s="95"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="49"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="40"/>
       <c r="L2" s="95"/>
       <c r="M2" s="95"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="49"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="40"/>
       <c r="T2" s="96"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="51"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="42"/>
       <c r="T3" s="97"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="53"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="53"/>
+      <c r="A4" s="69"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="45"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="45"/>
+      <c r="S4" s="44"/>
       <c r="T4" s="102"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
       <c r="A5" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="84" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="78"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="85"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="72"/>
+      <c r="T5" s="79"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
       <c r="A6" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="66" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="67"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="58"/>
+      <c r="Q6" s="58"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="60"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="66" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="67"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="P7" s="58"/>
+      <c r="Q7" s="58"/>
+      <c r="R7" s="58"/>
+      <c r="S7" s="58"/>
+      <c r="T7" s="60"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -11621,34 +11624,34 @@
       <c r="A15" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="40"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="40"/>
+      <c r="D15" s="56"/>
       <c r="E15" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="40"/>
+      <c r="F15" s="56"/>
       <c r="G15" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="56"/>
       <c r="J15" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="40"/>
+      <c r="K15" s="56"/>
       <c r="L15" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="56"/>
       <c r="O15" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="P15" s="58"/>
+      <c r="Q15" s="56"/>
       <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
@@ -11663,34 +11666,34 @@
       <c r="A16" s="103">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="40"/>
+      <c r="D16" s="56"/>
       <c r="E16" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="40"/>
+      <c r="F16" s="56"/>
       <c r="G16" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="56"/>
       <c r="J16" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="40"/>
+      <c r="K16" s="56"/>
       <c r="L16" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="56"/>
       <c r="O16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="56"/>
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="32"/>
@@ -11705,34 +11708,34 @@
       <c r="A17" s="103">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
+      <c r="B17" s="56"/>
       <c r="C17" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="40"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="104" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="40"/>
+      <c r="F17" s="56"/>
       <c r="G17" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="56"/>
       <c r="J17" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="40"/>
+      <c r="K17" s="56"/>
       <c r="L17" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="56"/>
       <c r="O17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="56"/>
       <c r="R17" s="31"/>
       <c r="S17" s="31"/>
       <c r="T17" s="32"/>
@@ -11745,22 +11748,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="103"/>
-      <c r="B18" s="40"/>
+      <c r="B18" s="56"/>
       <c r="C18" s="104"/>
-      <c r="D18" s="40"/>
+      <c r="D18" s="56"/>
       <c r="E18" s="104"/>
-      <c r="F18" s="40"/>
+      <c r="F18" s="56"/>
       <c r="G18" s="98"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="56"/>
       <c r="J18" s="98"/>
-      <c r="K18" s="40"/>
+      <c r="K18" s="56"/>
       <c r="L18" s="100"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="56"/>
       <c r="O18" s="100"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="56"/>
       <c r="R18" s="31"/>
       <c r="S18" s="31"/>
       <c r="T18" s="32"/>
@@ -11773,22 +11776,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="103"/>
-      <c r="B19" s="40"/>
+      <c r="B19" s="56"/>
       <c r="C19" s="104"/>
-      <c r="D19" s="40"/>
+      <c r="D19" s="56"/>
       <c r="E19" s="104"/>
-      <c r="F19" s="40"/>
+      <c r="F19" s="56"/>
       <c r="G19" s="98"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="56"/>
       <c r="J19" s="98"/>
-      <c r="K19" s="40"/>
+      <c r="K19" s="56"/>
       <c r="L19" s="100"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="56"/>
       <c r="O19" s="100"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="56"/>
       <c r="R19" s="31"/>
       <c r="S19" s="31"/>
       <c r="T19" s="32"/>
@@ -11801,22 +11804,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="103"/>
-      <c r="B20" s="40"/>
+      <c r="B20" s="56"/>
       <c r="C20" s="104"/>
-      <c r="D20" s="40"/>
+      <c r="D20" s="56"/>
       <c r="E20" s="104"/>
-      <c r="F20" s="40"/>
+      <c r="F20" s="56"/>
       <c r="G20" s="98"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="56"/>
       <c r="J20" s="98"/>
-      <c r="K20" s="40"/>
+      <c r="K20" s="56"/>
       <c r="L20" s="100"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="56"/>
       <c r="O20" s="100"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="56"/>
       <c r="R20" s="31"/>
       <c r="S20" s="31"/>
       <c r="T20" s="32"/>
@@ -11829,22 +11832,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="103"/>
-      <c r="B21" s="40"/>
+      <c r="B21" s="56"/>
       <c r="C21" s="104"/>
-      <c r="D21" s="40"/>
+      <c r="D21" s="56"/>
       <c r="E21" s="104"/>
-      <c r="F21" s="40"/>
+      <c r="F21" s="56"/>
       <c r="G21" s="98"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="56"/>
       <c r="J21" s="98"/>
-      <c r="K21" s="40"/>
+      <c r="K21" s="56"/>
       <c r="L21" s="100"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="56"/>
       <c r="O21" s="100"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="56"/>
       <c r="R21" s="31"/>
       <c r="S21" s="31"/>
       <c r="T21" s="32"/>
@@ -11857,22 +11860,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="103"/>
-      <c r="B22" s="40"/>
+      <c r="B22" s="56"/>
       <c r="C22" s="104"/>
-      <c r="D22" s="40"/>
+      <c r="D22" s="56"/>
       <c r="E22" s="104"/>
-      <c r="F22" s="40"/>
+      <c r="F22" s="56"/>
       <c r="G22" s="98"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="56"/>
       <c r="J22" s="98"/>
-      <c r="K22" s="40"/>
+      <c r="K22" s="56"/>
       <c r="L22" s="100"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="56"/>
       <c r="O22" s="100"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="56"/>
       <c r="R22" s="31"/>
       <c r="S22" s="31"/>
       <c r="T22" s="32"/>
@@ -11885,22 +11888,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="103"/>
-      <c r="B23" s="40"/>
+      <c r="B23" s="56"/>
       <c r="C23" s="104"/>
-      <c r="D23" s="40"/>
+      <c r="D23" s="56"/>
       <c r="E23" s="104"/>
-      <c r="F23" s="40"/>
+      <c r="F23" s="56"/>
       <c r="G23" s="98"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="56"/>
       <c r="J23" s="98"/>
-      <c r="K23" s="40"/>
+      <c r="K23" s="56"/>
       <c r="L23" s="100"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="56"/>
       <c r="O23" s="100"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="56"/>
       <c r="R23" s="31"/>
       <c r="S23" s="31"/>
       <c r="T23" s="32"/>
@@ -11913,22 +11916,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="103"/>
-      <c r="B24" s="40"/>
+      <c r="B24" s="56"/>
       <c r="C24" s="104"/>
-      <c r="D24" s="40"/>
+      <c r="D24" s="56"/>
       <c r="E24" s="104"/>
-      <c r="F24" s="40"/>
+      <c r="F24" s="56"/>
       <c r="G24" s="98"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="56"/>
       <c r="J24" s="98"/>
-      <c r="K24" s="40"/>
+      <c r="K24" s="56"/>
       <c r="L24" s="100"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="56"/>
       <c r="O24" s="100"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="56"/>
       <c r="R24" s="31"/>
       <c r="S24" s="31"/>
       <c r="T24" s="32"/>
@@ -11941,22 +11944,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="103"/>
-      <c r="B25" s="40"/>
+      <c r="B25" s="56"/>
       <c r="C25" s="104"/>
-      <c r="D25" s="40"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="104"/>
-      <c r="F25" s="40"/>
+      <c r="F25" s="56"/>
       <c r="G25" s="98"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="56"/>
       <c r="J25" s="98"/>
-      <c r="K25" s="40"/>
+      <c r="K25" s="56"/>
       <c r="L25" s="100"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="56"/>
       <c r="O25" s="100"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="56"/>
       <c r="R25" s="31"/>
       <c r="S25" s="31"/>
       <c r="T25" s="32"/>
@@ -11969,22 +11972,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="103"/>
-      <c r="B26" s="40"/>
+      <c r="B26" s="56"/>
       <c r="C26" s="104"/>
-      <c r="D26" s="40"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="104"/>
-      <c r="F26" s="40"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="98"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="56"/>
       <c r="J26" s="98"/>
-      <c r="K26" s="40"/>
+      <c r="K26" s="56"/>
       <c r="L26" s="100"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="56"/>
       <c r="O26" s="100"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="56"/>
       <c r="R26" s="31"/>
       <c r="S26" s="31"/>
       <c r="T26" s="32"/>
@@ -11997,22 +12000,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="103"/>
-      <c r="B27" s="40"/>
+      <c r="B27" s="56"/>
       <c r="C27" s="104"/>
-      <c r="D27" s="40"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="104"/>
-      <c r="F27" s="40"/>
+      <c r="F27" s="56"/>
       <c r="G27" s="98"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="56"/>
       <c r="J27" s="98"/>
-      <c r="K27" s="40"/>
+      <c r="K27" s="56"/>
       <c r="L27" s="100"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="56"/>
       <c r="O27" s="100"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="56"/>
       <c r="R27" s="31"/>
       <c r="S27" s="31"/>
       <c r="T27" s="32"/>
@@ -12025,22 +12028,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="103"/>
-      <c r="B28" s="40"/>
+      <c r="B28" s="56"/>
       <c r="C28" s="104"/>
-      <c r="D28" s="40"/>
+      <c r="D28" s="56"/>
       <c r="E28" s="104"/>
-      <c r="F28" s="40"/>
+      <c r="F28" s="56"/>
       <c r="G28" s="98"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="56"/>
       <c r="J28" s="98"/>
-      <c r="K28" s="40"/>
+      <c r="K28" s="56"/>
       <c r="L28" s="100"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="56"/>
       <c r="O28" s="100"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="56"/>
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="32"/>
@@ -12053,22 +12056,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="103"/>
-      <c r="B29" s="40"/>
+      <c r="B29" s="56"/>
       <c r="C29" s="104"/>
-      <c r="D29" s="40"/>
+      <c r="D29" s="56"/>
       <c r="E29" s="104"/>
-      <c r="F29" s="40"/>
+      <c r="F29" s="56"/>
       <c r="G29" s="98"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="56"/>
       <c r="J29" s="98"/>
-      <c r="K29" s="40"/>
+      <c r="K29" s="56"/>
       <c r="L29" s="100"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="56"/>
       <c r="O29" s="100"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="56"/>
       <c r="R29" s="31"/>
       <c r="S29" s="31"/>
       <c r="T29" s="32"/>
@@ -12081,22 +12084,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="103"/>
-      <c r="B30" s="40"/>
+      <c r="B30" s="56"/>
       <c r="C30" s="104"/>
-      <c r="D30" s="40"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="104"/>
-      <c r="F30" s="40"/>
+      <c r="F30" s="56"/>
       <c r="G30" s="98"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="56"/>
       <c r="J30" s="98"/>
-      <c r="K30" s="40"/>
+      <c r="K30" s="56"/>
       <c r="L30" s="100"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="56"/>
       <c r="O30" s="100"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="56"/>
       <c r="R30" s="31"/>
       <c r="S30" s="31"/>
       <c r="T30" s="32"/>
@@ -12109,22 +12112,22 @@
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
       <c r="A31" s="106"/>
-      <c r="B31" s="70"/>
+      <c r="B31" s="63"/>
       <c r="C31" s="107"/>
-      <c r="D31" s="70"/>
+      <c r="D31" s="63"/>
       <c r="E31" s="107"/>
-      <c r="F31" s="70"/>
+      <c r="F31" s="63"/>
       <c r="G31" s="99"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="70"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="63"/>
       <c r="J31" s="99"/>
-      <c r="K31" s="70"/>
+      <c r="K31" s="63"/>
       <c r="L31" s="101"/>
-      <c r="M31" s="69"/>
-      <c r="N31" s="70"/>
+      <c r="M31" s="62"/>
+      <c r="N31" s="63"/>
       <c r="O31" s="101"/>
-      <c r="P31" s="69"/>
-      <c r="Q31" s="70"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="63"/>
       <c r="R31" s="34"/>
       <c r="S31" s="34"/>
       <c r="T31" s="35"/>
